--- a/processed_ruby_restored_xlsx/sc212_ノノ４：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc212_ノノ４：花火.ss.xlsx
@@ -590,7 +590,8 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>「Uh, well, um… about, uh, what happened today… right？」</t>
+          <t>「Uh, well, um… about, uh, what happened today…
+right？」</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -620,9 +621,9 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>The atmosphere had become one where we were both aware
-of each other, so I completely felt like words weren’t
-needed.</t>
+          <t>The atmosphere had become one where we were both
+aware of each other, so I completely felt like words
+weren’t needed.</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -667,7 +668,8 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, shall we watch the fireworks together tonight？」</t>
+          <t>「Yeah, shall we watch the fireworks together
+tonight？」</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -819,9 +821,9 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's reaction made me blush too, and I couldn't
-help but give a look that showed I was hoping for
-something.</t>
+          <t>Nono-chan's reaction made me blush too, and I
+couldn't help but give a look that showed I was
+hoping for something.</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1171,8 +1173,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Rin narrowed her eyes at our way over-the-top reaction
-and gave a little nod.</t>
+          <t>Rin narrowed her eyes at our way over-the-top
+reaction and gave a little nod.</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1618,8 +1620,8 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>Only now did she probably recall the earlier situation
-and think the same way I did.</t>
+          <t>Only now did she probably recall the earlier
+situation and think the same way I did.</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1772,8 +1774,8 @@
       <c r="B86" s="1" t="inlineStr">
         <is>
           <t>Still, I guess we'd end up noticing each other no
-matter what, so maybe it's better if we purposely work
-separately.</t>
+matter what, so maybe it's better if we purposely
+work separately.</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1849,7 +1851,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... I think it's just a bit of a walk from here.」</t>
+          <t>「Yeah... I think it's just a bit of a walk from
+here.」</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1864,8 +1867,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Once we started walking, the yukata I'd put on after a
-long time felt kind of awkward.</t>
+          <t>Once we started walking, the yukata I'd put on after
+a long time felt kind of awkward.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2017,7 +2020,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>「No, not at all — it really suits you and you're cute」</t>
+          <t>「No, not at all — it really suits you and you're
+cute」</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2110,8 +2114,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei！ Please hurry！ The fireworks are about
-to start！」</t>
+          <t>「Janitor-sensei！ Please hurry！ The fireworks are
+about to start！」</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2479,8 +2483,8 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>For some reason I got nervous too, and I squeezed back
-hard.</t>
+          <t>For some reason I got nervous too, and I squeezed
+back hard.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2921,8 +2925,8 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>I crouched down and lifted my gaze because I wanted to
-share the same wonder Nono-chan was feeling.</t>
+          <t>I crouched down and lifted my gaze because I wanted
+to share the same wonder Nono-chan was feeling.</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2937,9 +2941,9 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>As the visible sky seemed to stretch farther away, the
-vivid fireworks spreading across it felt even more
-moving.</t>
+          <t>As the visible sky seemed to stretch farther away,
+the vivid fireworks spreading across it felt even
+more moving.</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3076,8 +3080,8 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>Maybe noticing my gaze, Nono-chan quietly turns to the
-side.</t>
+          <t>Maybe noticing my gaze, Nono-chan quietly turns to
+the side.</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3473,7 +3477,8 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>「Fwah！ Hey, mui-sensei！ Chu...chu！ Nn-ah, chuu...chu！」</t>
+          <t>「Fwah！ Hey, mui-sensei！ Chu...chu！ Nn-ah,
+chuu...chu！」</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3582,8 +3587,8 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>It's like she's throwing the thrill of fireworks at me
-in the form of kisses.</t>
+          <t>It's like she's throwing the thrill of fireworks at
+me in the form of kisses.</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3643,8 +3648,8 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>「Hah！ Ah... Mui-sensei！ Smooch... nchuu！ Chup, lick...
-aaahn！」</t>
+          <t>「Hah！ Ah... Mui-sensei！ Smooch... nchuu！ Chup,
+lick... aaahn！」</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3676,7 +3681,8 @@
       <c r="B210" s="1" t="inlineStr">
         <is>
           <t>The feel of the saliva seemed hotter than usual —
-maybe because her tiny body was already getting ready.</t>
+maybe because her tiny body was already getting
+ready.</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3969,8 +3975,8 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... mwah！ mwah！ It's because of Mui-sensei... mmm,
-mwah！」</t>
+          <t>「Ahh... mwah！ mwah！ It's because of Mui-sensei...
+mmm, mwah！」</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -4062,8 +4068,8 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>Of course, I'm happy with anything as long as I'm with
-Nono-chan.</t>
+          <t>Of course, I'm happy with anything as long as I'm
+with Nono-chan.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4708,8 +4714,8 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>It feels wrong to suddenly blurt out that I want to do
-something sexy.</t>
+          <t>It feels wrong to suddenly blurt out that I want to
+do something sexy.</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4725,8 +4731,8 @@
       <c r="B278" s="1" t="inlineStr">
         <is>
           <t>So, about continuing from the other day... or so I
-said, but Nono-chan nodded more straightforwardly than
-I’d expected.</t>
+said, but Nono-chan nodded more straightforwardly
+than I’d expected.</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4818,8 +4824,8 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>…With a touch of bashfulness, they deliberately say it
-out loud as they pull down their pants.</t>
+          <t>…With a touch of bashfulness, they deliberately say
+it out loud as they pull down their pants.</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4880,8 +4886,8 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>...The exposed penis was rock-hard, as if to prove the
-point.</t>
+          <t>...The exposed penis was rock-hard, as if to prove
+the point.</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -5293,8 +5299,8 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>Honestly, I wanted her to take it into her mouth right
-away.</t>
+          <t>Honestly, I wanted her to take it into her mouth
+right away.</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5523,8 +5529,9 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>Then Nono-chan, carried by the momentum, kept pressing
-her little mouth to my penis again and again.</t>
+          <t>Then Nono-chan, carried by the momentum, kept
+pressing her little mouth to my penis again and
+again.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5690,8 +5697,8 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>When the pleasure stopped for a moment, the excitement
-skated up and I got into a spiteful mood.</t>
+          <t>When the pleasure stopped for a moment, the
+excitement skated up and I got into a spiteful mood.</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -6026,8 +6033,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>She let saliva run down and let thick saliva drip onto
-my penis.</t>
+          <t>She let saliva run down and let thick saliva drip
+onto my penis.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6163,8 +6170,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... heehee！ Janitor-sensei taught me so carefully,
-you know...？」</t>
+          <t>「Mmm... heehee！ Janitor-sensei taught me so
+carefully, you know...？」</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6530,8 +6537,8 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan teases and torments my penis while egging me
-on.</t>
+          <t>Nono-chan teases and torments my penis while egging
+me on.</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6899,8 +6906,8 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>Mixing in a bit of irritation, Nono-chan's tongue work
-kept getting more intense.</t>
+          <t>Mixing in a bit of irritation, Nono-chan's tongue
+work kept getting more intense.</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -6946,8 +6953,8 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>「When I lick here... nn, chu, nng！ It's getting... ah,
-it's getting hot... fuhaa...！」</t>
+          <t>「When I lick here... nn, chu, nng！ It's getting...
+ah, it's getting hot... fuhaa...！」</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -7007,8 +7014,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Sweating is...good for your health, you know？ Churuu,
-pero... chu, chu！」</t>
+          <t>「Sweating is...good for your health, you know？
+Churuu, pero... chu, chu！」</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7298,8 +7305,8 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>Like my words had struck a match, her mouthwork shifts
-into a wet, intense assault.</t>
+          <t>Like my words had struck a match, her mouthwork
+shifts into a wet, intense assault.</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7345,8 +7352,8 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>「Mwah, ah, mwah！ Janitor-sensei, you're getting such a
-naughty look...！」</t>
+          <t>「Mwah, ah, mwah！ Janitor-sensei, you're getting such
+a naughty look...！」</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -8020,8 +8027,8 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>「I-Is that so...？ Well then... I'll make you even more
-tingly... *munch*！ Ah, fchuuuuu！」</t>
+          <t>「I-Is that so...？ Well then... I'll make you even
+more tingly... *munch*！ Ah, fchuuuuu！」</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8267,7 +8274,8 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>「Chu... churu！ Next is... here！ Chu... chupa！ Chupuu！」</t>
+          <t>「Chu... churu！ Next is... here！ Chu... chupa！
+Chupuu！」</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8312,8 +8320,8 @@
       </c>
       <c r="B512" s="1" t="inlineStr">
         <is>
-          <t>Her sexy tongue catches the frenulum and goes back and
-forth continuously.</t>
+          <t>Her sexy tongue catches the frenulum and goes back
+and forth continuously.</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8405,8 +8413,8 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>With attacks that speed up and slow down, I don't even
-get a moment to catch my breath.</t>
+          <t>With attacks that speed up and slow down, I don't
+even get a moment to catch my breath.</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8651,7 +8659,8 @@
       <c r="B534" s="1" t="inlineStr">
         <is>
           <t>It’s the same kind of back-and-forth as before, but
-the excitement just builds to a whole different level.</t>
+the excitement just builds to a whole different
+level.</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -8681,8 +8690,8 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>「W-well then... here I go... here I go...! Hamu—! Amu!
-Nn! Nmm!」</t>
+          <t>「W-well then... here I go... here I go...! Hamu—!
+Amu! Nn! Nmm!」</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8744,8 +8753,8 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>The soft pressure was just right, and inside that tiny
-mouth, the penis swelled even more.</t>
+          <t>The soft pressure was just right, and inside that
+tiny mouth, the penis swelled even more.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8912,8 +8921,8 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>When pushing it back in, tighten up hard so the glans'
-rim catches.</t>
+          <t>When pushing it back in, tighten up hard so the
+glans' rim catches.</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -9051,8 +9060,8 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>She really tries to make me come using only her mouth,
-her tongue winding around thickly too.</t>
+          <t>She really tries to make me come using only her
+mouth, her tongue winding around thickly too.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9392,8 +9401,8 @@
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
-          <t>This is going to be a big mess, but my penis begins to
-ejaculate without holding back...！</t>
+          <t>This is going to be a big mess, but my penis begins
+to ejaculate without holding back...！</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -9728,8 +9737,8 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... oh no, what should we do... my precious yukata
-is all sticky...」</t>
+          <t>「Mmm... oh no, what should we do... my precious
+yukata is all sticky...」</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -9805,8 +9814,9 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>Even though Nono-chan had her precious yukata dirtied,
-she didn't get that angry because she trusted me.</t>
+          <t>Even though Nono-chan had her precious yukata
+dirtied, she didn't get that angry because she
+trusted me.</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9836,8 +9846,8 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>「N... Nono-chan？ So, I hate to call it just an excuse,
-but, um...」</t>
+          <t>「N... Nono-chan？ So, I hate to call it just an
+excuse, but, um...」</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9990,7 +10000,8 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「Ah, um... so, Janitor-sensei... what should I do...？」</t>
+          <t>「Ah, um... so, Janitor-sensei... what should I
+do...？」</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10113,7 +10124,8 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaah... wearing this outfit is so embarrassing...！」</t>
+          <t>「Fuwaah... wearing this outfit is so
+embarrassing...！」</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -10204,8 +10216,8 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... I think it's less embarrassing than when you
-had it in your mouth...？」</t>
+          <t>「Ahaha... I think it's less embarrassing than when
+you had it in your mouth...？」</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -10405,7 +10417,8 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nngh... I have to be the one to start, right...？」</t>
+          <t>「Nn, nngh... I have to be the one to start,
+right...？」</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10481,8 +10494,8 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan is only confused by her first time in the
-cowgirl position.</t>
+          <t>...Nono-chan is only confused by her first time in
+the cowgirl position.</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -10574,8 +10587,8 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>I said it with a worried look, and Nono-chan shook her
-head and, if anything, showed an even more
+          <t>I said it with a worried look, and Nono-chan shook
+her head and, if anything, showed an even more
 enthusiastic air.</t>
         </is>
       </c>
@@ -10652,8 +10665,8 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan readjusted the penis in her hand and pressed
-it against her between (my/her) legs….</t>
+          <t>Nono-chan readjusted the penis in her hand and
+pressed it against her between (my/her) legs….</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -11447,7 +11460,8 @@
       </c>
       <c r="B716" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Hah... yes！ I-I-I'm okay... really, I'm okay...！」</t>
+          <t>「Ah！ Hah... yes！ I-I-I'm okay... really, I'm
+okay...！」</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11462,7 +11476,8 @@
       </c>
       <c r="B717" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan blushes bright red and puts on a brave face.</t>
+          <t>Nono-chan blushes bright red and puts on a brave
+face.</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -11569,8 +11584,8 @@
       </c>
       <c r="B724" s="1" t="inlineStr">
         <is>
-          <t>For some reason, it even looks like she's trying extra
-hard.</t>
+          <t>For some reason, it even looks like she's trying
+extra hard.</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -11891,8 +11906,8 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>...This is the third time I'm asked if she's okay, but
-Nono-chan's reply is as pained as ever.</t>
+          <t>...This is the third time I'm asked if she's okay,
+but Nono-chan's reply is as pained as ever.</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -11968,7 +11983,8 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan looked back at me and gave a ticklish smile.</t>
+          <t>Nono-chan looked back at me and gave a ticklish
+smile.</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -12210,8 +12226,8 @@
       </c>
       <c r="B766" s="1" t="inlineStr">
         <is>
-          <t>When I properly tell her that it feels good, Nono-chan
-smiles happily.</t>
+          <t>When I properly tell her that it feels good,
+Nono-chan smiles happily.</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -12287,8 +12303,8 @@
       </c>
       <c r="B771" s="1" t="inlineStr">
         <is>
-          <t>Maybe it would be nice to just lie here and let things
-happen to me.</t>
+          <t>Maybe it would be nice to just lie here and let
+things happen to me.</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -12379,8 +12395,8 @@
       </c>
       <c r="B777" s="1" t="inlineStr">
         <is>
-          <t>What suddenly jumps into my view is a tiny body lit by
-the fireworks.</t>
+          <t>What suddenly jumps into my view is a tiny body lit
+by the fireworks.</t>
         </is>
       </c>
       <c r="C777" t="n">
@@ -12563,8 +12579,8 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>But she doesn't seem able to resist the stimulation to
-her pussy, and her hands are unsteady.</t>
+          <t>But she doesn't seem able to resist the stimulation
+to her pussy, and her hands are unsteady.</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -13366,8 +13382,8 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>「...In this position, you can really see where they're
-connected, can't you...？」</t>
+          <t>「...In this position, you can really see where
+they're connected, can't you...？」</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13752,8 +13768,8 @@
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
-          <t>「Nnnuu...! B-but, b-but... it feels so good...!？ Nfuu,
-fuuu...!」</t>
+          <t>「Nnnuu...! B-but, b-but... it feels so good...!？
+Nfuu, fuuu...!」</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -13937,8 +13953,8 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>「It’s amazing...！ Nono-chan！ Aahh！ It feels so good...
-ha, uhaa！」</t>
+          <t>「It’s amazing...！ Nono-chan！ Aahh！ It feels so
+good... ha, uhaa！」</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -14060,8 +14076,8 @@
       </c>
       <c r="B886" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan’s loud voice seemed like it could even drown
-out the thunder of the fireworks.</t>
+          <t>Nono-chan’s loud voice seemed like it could even
+drown out the thunder of the fireworks.</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -14184,8 +14200,8 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>「Ahh, nngh！ Oh—Mui-sensei！ Ah, hah！ Aah... nngh！ Nngh！
-Nngh！ Nngh！」</t>
+          <t>「Ahh, nngh！ Oh—Mui-sensei！ Ah, hah！ Aah... nngh！
+Nngh！ Nngh！ Nngh！」</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -14245,8 +14261,8 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>That turned it into long, deep thrusts, and a pleasure
-unlike anything before washed over her...！</t>
+          <t>That turned it into long, deep thrusts, and a
+pleasure unlike anything before washed over her...！</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -15210,7 +15226,8 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan completely slumped and let her body go limp.</t>
+          <t>Nono-chan completely slumped and let her body go
+limp.</t>
         </is>
       </c>
       <c r="C961" t="n">

--- a/processed_ruby_restored_xlsx/sc212_ノノ４：花火.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc212_ノノ４：花火.ss.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>「Y-yo, Janitor-sensei...」</t>
+          <t>Y-yo, Janitor-sensei...</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -590,8 +590,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>「Uh, well, um… about, uh, what happened today…
-right？」</t>
+          <t>Uh, well, um… about, uh, what happened today… right？</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -745,8 +744,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>「Ahahaha... but you figured it out so well, didn't
-you~？」</t>
+          <t>Ahahaha... but you figured it out so well, didn」t
+you~？</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -776,7 +775,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>「W-well… you know, we did promise, after all…」</t>
+          <t>W-well… you know, we did promise, after all…</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1249,7 +1248,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>「...Janitor-sensei？ Do your eyes hurt？」</t>
+          <t>...Janitor-sensei？ Do your eyes hurt？</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1467,7 +1466,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>「Mm... Janitor-sensei seems fine, doesn't he？」</t>
+          <t>Mm... Janitor-sensei seems fine, doesn't he？</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1757,7 +1756,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>...I said 'as usual,' but I didn't have to be so
+          <t>...I said 'as usual,' but he didn't have to be so
 dutiful about making it literally 'as usual'.</t>
         </is>
       </c>
@@ -2114,8 +2113,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei！ Please hurry！ The fireworks are
-about to start！」</t>
+          <t>Janitor-sensei！ Please hurry！ The fireworks are about
+to start！</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2834,7 +2833,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>「Amazing！ Really amazing, Janitor-sensei！」</t>
+          <t>Amazing！ Really amazing, Janitor-sensei！</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -3035,7 +3034,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Janitor-sensei...」</t>
+          <t>Ah... Janitor-sensei...</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4439,7 +4438,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>「Hahwaa…！ Just from a chu~ and already like this…」</t>
+          <t>Hahwaa…！ Just from a chu~ and already like this…</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4561,7 +4560,7 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>「W-wait a sec！ Stop... y-you're being too rough...」</t>
+          <t>W-wait a sec！ Stop... y-you're being too rough...</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4606,7 +4605,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>When I said 'stop', she pulled her whole body away
+          <t>When I said 'stop', they pulled their whole body away
 from me in an instant.</t>
         </is>
       </c>
@@ -4871,7 +4870,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah... it's really big, isn't it...」</t>
+          <t>Y-yeah... it's really big, isn't it...</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -5637,7 +5636,7 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t>「Hafu—！ I somehow feel so dirty... nngh, nnghh...！」</t>
+          <t>Hafu—！ I somehow feel so dirty... nngh, nnghh...！</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5728,8 +5727,8 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>「Um... well... I really don't think you should say
-things like that...！」</t>
+          <t>Um... well... I really don't think you should say
+things like that...！</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -6034,7 +6033,7 @@
       <c r="B363" s="1" t="inlineStr">
         <is>
           <t>She let saliva run down and let thick saliva drip
-onto my penis.</t>
+onto his penis.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6079,7 +6078,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>When Nono-chan's hot saliva touched it, my penis
+          <t>When Nono-chan's hot saliva touched it, his penis
 twitched and started to shudder.</t>
         </is>
       </c>
@@ -6323,7 +6322,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>Just that alone, my penis was enveloped in even
+          <t>Just that alone, his penis was enveloped in even
 greater pleasure.</t>
         </is>
       </c>
@@ -7061,7 +7060,7 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>I was being toyed with however she wanted.</t>
+          <t>He was being toyed with however she wanted.</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -7322,7 +7321,7 @@
       <c r="B447" s="1" t="inlineStr">
         <is>
           <t>A shameless trickle of arousal leaks from the tip of
-my penis, the pleasure swelling by the second.</t>
+her penis, the pleasure swelling by the second.</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7383,8 +7382,7 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>「Haa, haaah！ It feels so good… ugh！ I'm gonna lose
-it…」</t>
+          <t>Haa, haaah！ It feels so good… ugh！ I'm gonna lose it…</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7950,8 +7948,8 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>「When you beg me like that, it makes me all tingly...
-you know.」</t>
+          <t>When you beg me like that, it makes me all tingly...
+you know.</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -8228,7 +8226,7 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaa... it's coming！ It feels so good... ah！」</t>
+          <t>Uwaaa... it's coming！ It feels so good... ah！</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8274,8 +8272,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>「Chu... churu！ Next is... here！ Chu... chupa！
-Chupuu！」</t>
+          <t>Chu... churu！ Next is... here！ Chu... chupa！ Chupuu！</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8305,7 +8302,7 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>「Uah, aahhh... huf！ Ugh, haha！」</t>
+          <t>Uah, aahhh... huf！ Ugh, haha！</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8367,7 +8364,7 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>「N~uu, chupaa... n, chuu, chu, ...fuu, ah, chuuu...」</t>
+          <t>N~uu, chupaa... n, chuu, chu, ...fuu, ah, chuuu...</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8475,7 +8472,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>「Huh...？ Ah... yeah, it's working properly...」</t>
+          <t>Huh...？ Ah... yeah, it's working properly...</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8521,7 +8518,7 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>「Is that so...！ I'm so glad...！」</t>
+          <t>Is that so...！ I'm so glad...！</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8875,7 +8872,7 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, fgh！ Ugh, ahhh...！」</t>
+          <t>Ugh, fgh！ Ugh, ahhh...！</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -9507,8 +9504,8 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>「Fua！ So many hot things... they're coming in lots,
-y'know~」</t>
+          <t>Fua！ So many hot things... they're coming in lots,
+y'know~</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -10000,8 +9997,7 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「Ah, um... so, Janitor-sensei... what should I
-do...？」</t>
+          <t>Ah, um... so, Janitor-sensei... what should I do...？</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10968,7 +10964,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>「Nnff—！？ Nngh, nnaaahh…！」</t>
+          <t>Nnff—！？ Nngh, nnaaahh…！</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -11291,8 +11287,8 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei... your penis—ha！—it's already
-inside... fwaa！」</t>
+          <t>Janitor-sensei... your penis—ha！—it's already
+inside... fwaa！</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11906,7 +11902,7 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>...This is the third time I'm asked if she's okay,
+          <t>...This is the third time he's asked if she's okay,
 but Nono-chan's reply is as pained as ever.</t>
         </is>
       </c>
@@ -12350,7 +12346,7 @@
       </c>
       <c r="B774" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh... Janitor-sensei, ahah！」</t>
+          <t>Heh heh... Janitor-sensei, ahah！</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -13085,8 +13081,8 @@
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>「No...！ My boobs... I'm touching them... aaah！ Nnh！
-Yoo, mui-sensee...！」</t>
+          <t>No...！ My boobs... he's touching them... aaah！ Nnh！
+Yoo, mui-sensee...！</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -13552,8 +13548,8 @@
       </c>
       <c r="B852" s="1" t="inlineStr">
         <is>
-          <t>「Phew... fuaa！ Ah！ Penis... nn！ Phew！ Fwaaah... ah,
-ah！」</t>
+          <t>Phew... fuaa！ Ah！ Penis... nn！ Phew！ Fwaaah... ah,
+ah！</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -14107,8 +14103,8 @@
       </c>
       <c r="B888" s="1" t="inlineStr">
         <is>
-          <t>「No！ N-no… I'm going to lose it, nn！ Ahh！ Hah…！ Huh,
-huhu…！」</t>
+          <t>No！ N-no… I'm going to lose it, nn！ Ahh！ Hah…！ Huh,
+huhu…！</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -14138,7 +14134,7 @@
       </c>
       <c r="B890" s="1" t="inlineStr">
         <is>
-          <t>「Huh, ahh！ Haha, ah！」</t>
+          <t>Huh, ahh！ Haha, ah！</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -14200,8 +14196,8 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>「Ahh, nngh！ Oh—Mui-sensei！ Ah, hah！ Aah... nngh！
-Nngh！ Nngh！ Nngh！」</t>
+          <t>Ahh, nngh！ Oh—Mui-sensei！ Ah, hah！ Aah... nngh！ Nngh！
+Nngh！ Nngh！</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -14672,7 +14668,7 @@
       </c>
       <c r="B925" s="1" t="inlineStr">
         <is>
-          <t>「Haaahn！ My stomach—ah！ It's coming, uaaa...」</t>
+          <t>Haaahn！ My stomach—ah！ It's coming, uaaa...</t>
         </is>
       </c>
       <c r="C925" t="n">
@@ -14703,7 +14699,7 @@
       </c>
       <c r="B927" s="1" t="inlineStr">
         <is>
-          <t>Each time her vaginal muscles clench tight, I've
+          <t>Each time her vaginal muscles clench tight, he's
 driven deeper and deeper into her pussy.</t>
         </is>
       </c>
@@ -14734,8 +14730,8 @@
       </c>
       <c r="B929" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ So good—nngh, fuh！ My stomach…it’s so hot—！ It’s
-coming so much…」</t>
+          <t>Ah！ So good—nngh, fuh！ My stomach…it’s so hot—！ It’s
+coming so much…</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -14796,7 +14792,7 @@
       </c>
       <c r="B933" s="1" t="inlineStr">
         <is>
-          <t>「Haa, uaa... I'm getting all weird...」</t>
+          <t>Haa, uaa... I'm getting all weird...</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -15148,7 +15144,7 @@
       </c>
       <c r="B956" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah... my tummy's full, but...」</t>
+          <t>Fwaaah... my tummy's full, but...</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -15163,8 +15159,8 @@
       </c>
       <c r="B957" s="1" t="inlineStr">
         <is>
-          <t>The shock of her hips dropping with gravity made the
-semen still in the urethra get expelled.</t>
+          <t>The shock of their hips dropping with gravity made
+the semen still in the urethra get expelled.</t>
         </is>
       </c>
       <c r="C957" t="n">
